--- a/data/trans_orig/P41C_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41C_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han tenido o tienen dificultades para tener un embarazo en 2023</t>
+          <t>Población según si han tenido o tienen dificultades para tener un embarazo en 2023 (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127749</t>
+          <t>129144</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144755</t>
+          <t>144964</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>153520</t>
+          <t>153242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158239</t>
+          <t>158176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284902</t>
+          <t>284187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>302035</t>
+          <t>302214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>474160</t>
+          <t>474364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>491299</t>
+          <t>491068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>226889</t>
+          <t>227422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238870</t>
+          <t>238902</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>705614</t>
+          <t>705032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>732002</t>
+          <t>731681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13135</t>
+          <t>14274</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10865</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74357</t>
+          <t>74082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83098</t>
+          <t>83315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98820</t>
+          <t>98812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106982</t>
+          <t>106870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>177558</t>
+          <t>175690</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>188828</t>
+          <t>188730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140189</t>
+          <t>139649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152172</t>
+          <t>151899</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164515</t>
+          <t>164928</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175743</t>
+          <t>175806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>309475</t>
+          <t>309869</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>325001</t>
+          <t>325721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>20417</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>835103</t>
+          <t>835387</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>868457</t>
+          <t>869304</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>655429</t>
+          <t>655196</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>674208</t>
+          <t>673870</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1498957</t>
+          <t>1499311</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1541807</t>
+          <t>1539506</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22527</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39247</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,47 +3960,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>20368</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>10907</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>34389</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>20368</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>10278</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>33807</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41C_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>140148</t>
+          <t>145787</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129144</t>
+          <t>131781</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144964</t>
+          <t>150852</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>156621</t>
+          <t>167178</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>153242</t>
+          <t>163922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158176</t>
+          <t>168861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>296769</t>
+          <t>312965</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284187</t>
+          <t>297823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>302214</t>
+          <t>319169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>345</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>345</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>559</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>559</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>21422</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>22980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>147092</t>
+          <t>153434</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147092</t>
+          <t>153434</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147092</t>
+          <t>153434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>158839</t>
+          <t>169418</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>158839</t>
+          <t>169418</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>158839</t>
+          <t>169418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>305931</t>
+          <t>322852</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>305931</t>
+          <t>322852</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>305931</t>
+          <t>322852</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>485390</t>
+          <t>269864</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>474364</t>
+          <t>262512</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>491068</t>
+          <t>273515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>233979</t>
+          <t>257747</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>227422</t>
+          <t>249754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238902</t>
+          <t>263441</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>719369</t>
+          <t>527609</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>705032</t>
+          <t>518567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>731681</t>
+          <t>535138</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18938</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>663</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>663</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>491937</t>
+          <t>276391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>491937</t>
+          <t>276391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>491937</t>
+          <t>276391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>246053</t>
+          <t>271789</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>246053</t>
+          <t>271789</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>246053</t>
+          <t>271789</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>737990</t>
+          <t>548179</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>737990</t>
+          <t>548179</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>737990</t>
+          <t>548179</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>80177</t>
+          <t>90196</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74082</t>
+          <t>83523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83315</t>
+          <t>93663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>104035</t>
+          <t>127149</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98812</t>
+          <t>121062</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106870</t>
+          <t>130262</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,27 +2159,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>184213</t>
+          <t>217345</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>175690</t>
+          <t>209566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>188730</t>
+          <t>222448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2541,102 +2541,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>1132</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5665</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5648</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5321</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5105</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>6875</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>6619</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>84539</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84539</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84539</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>108878</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>108878</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108878</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>193417</t>
+          <t>227972</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>193417</t>
+          <t>227972</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>193417</t>
+          <t>227972</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>147212</t>
+          <t>161353</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139649</t>
+          <t>153177</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151899</t>
+          <t>166141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>171206</t>
+          <t>189754</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164928</t>
+          <t>182996</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175806</t>
+          <t>194355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>318417</t>
+          <t>351107</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>309869</t>
+          <t>342162</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>325721</t>
+          <t>358113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>12026</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>11964</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>155851</t>
+          <t>170087</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>155851</t>
+          <t>170087</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>155851</t>
+          <t>170087</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>181509</t>
+          <t>200261</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>181509</t>
+          <t>200261</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>181509</t>
+          <t>200261</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>337359</t>
+          <t>370348</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>337359</t>
+          <t>370348</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>337359</t>
+          <t>370348</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>852928</t>
+          <t>667199</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>835387</t>
+          <t>649949</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>869304</t>
+          <t>677410</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>665842</t>
+          <t>741827</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>655196</t>
+          <t>731327</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>673870</t>
+          <t>750506</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1518768</t>
+          <t>1409027</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1499311</t>
+          <t>1389789</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1539506</t>
+          <t>1422551</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,57 +3576,57 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>7932</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3225</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>6960</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>37965</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,27 +3862,27 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34389</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
